--- a/outputs/monitor_xlsx/20260330.xlsx
+++ b/outputs/monitor_xlsx/20260330.xlsx
@@ -544,10 +544,6 @@
           <t>-0.68%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.68%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-2.25%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+1.76%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.16%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>-4.23%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-1.42%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+4.75%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-639.37億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-206.06億</t>
@@ -807,7 +769,6 @@
           <t>32.07億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>37.26億</t>
@@ -818,8 +779,6 @@
           <t>186.28億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>122.29%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.91%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-741.29億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>8340口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8511口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>6.01億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>5.16億</t>
@@ -1016,10 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2223,6 +2165,112 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7675</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="E19" t="n">
+        <v>127</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G19" t="n">
+        <v>98</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-124</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>296</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1439</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-8985</v>
+      </c>
+      <c r="N19" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3136</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>382</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-735</v>
+      </c>
+      <c r="H20" t="n">
+        <v>180</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1340</v>
+      </c>
+      <c r="J20" t="n">
+        <v>192</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2591</v>
+      </c>
+      <c r="L20" t="n">
+        <v>13910</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-106305</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260330.xlsx
+++ b/outputs/monitor_xlsx/20260330.xlsx
@@ -536,14 +536,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33112.59</t>
+          <t>32518.16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68%</t>
-        </is>
-      </c>
+          <t>-1.80%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,14 +562,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>325.0</t>
+          <t>320.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+0.68%</t>
-        </is>
-      </c>
+          <t>-1.42%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +591,11 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -605,6 +618,10 @@
           <t>-2.25%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,14 +636,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4571.2$</t>
+          <t>4526.0$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+1.76%</t>
-        </is>
-      </c>
+          <t>+0.76%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -649,6 +670,10 @@
           <t>+0.16%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -671,6 +696,10 @@
           <t>-4.23%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -693,6 +722,10 @@
           <t>-1.42%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,14 +740,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104.37$</t>
+          <t>102.88$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+4.75%</t>
-        </is>
-      </c>
+          <t>+3.25%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -732,24 +769,25 @@
           <t>-639.37億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-206.06億</t>
+          <t>-166.09億</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1030.29億</t>
+          <t>-830.44億</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-411.77億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-8235.31億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -769,16 +807,19 @@
           <t>32.07億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.26億</t>
+          <t>22.6億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>186.28億</t>
-        </is>
-      </c>
+          <t>113.0億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -793,14 +834,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>122.29%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.91%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,6 +863,11 @@
           <t>-741.29億</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -835,11 +885,15 @@
           <t>8340口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8511口</t>
-        </is>
-      </c>
+          <t>8159口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,24 +911,25 @@
           <t>6.01億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.16億</t>
+          <t>-3.35億</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25.79億</t>
+          <t>-16.77億</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.35億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-147.03億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -921,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-206.06億</t>
+          <t>-166.09億</t>
         </is>
       </c>
     </row>
@@ -933,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1030.29億</t>
+          <t>-830.44億</t>
         </is>
       </c>
     </row>
@@ -945,7 +1000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-411.77億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -957,9 +1012,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-8235.31億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -969,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>37.26億</t>
+          <t>22.6億</t>
         </is>
       </c>
     </row>
@@ -981,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>186.28億</t>
+          <t>113.0億</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1059,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5.16億</t>
+          <t>-3.35億</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1071,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25.79億</t>
+          <t>-16.77億</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-7.35億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-147.03億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1126,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8511口</t>
+          <t>8159口</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1100,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1117,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1196,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1264,13 +1316,13 @@
         <v>-70742</v>
       </c>
       <c r="H4" t="n">
-        <v>-203280</v>
+        <v>-115466</v>
       </c>
       <c r="I4" t="n">
         <v>1900</v>
       </c>
       <c r="J4" t="n">
-        <v>1330</v>
+        <v>-1770</v>
       </c>
       <c r="K4" t="n">
         <v>47712</v>
@@ -1279,20 +1331,12 @@
         <v>14406</v>
       </c>
       <c r="M4" t="n">
-        <v>66878</v>
+        <v>52790</v>
       </c>
       <c r="N4" t="n">
         <v>-4579297</v>
       </c>
-      <c r="O4" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1327,13 +1371,13 @@
         <v>304</v>
       </c>
       <c r="H5" t="n">
-        <v>-1447</v>
+        <v>-1011</v>
       </c>
       <c r="I5" t="n">
         <v>-437</v>
       </c>
       <c r="J5" t="n">
-        <v>-415</v>
+        <v>-418</v>
       </c>
       <c r="K5" t="n">
         <v>112</v>
@@ -1342,20 +1386,12 @@
         <v>2785</v>
       </c>
       <c r="M5" t="n">
-        <v>14104</v>
+        <v>11154</v>
       </c>
       <c r="N5" t="n">
         <v>-78891</v>
       </c>
-      <c r="O5" t="n">
-        <v>-6.42</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1390,13 +1426,13 @@
         <v>-842</v>
       </c>
       <c r="H6" t="n">
-        <v>2222</v>
+        <v>4728</v>
       </c>
       <c r="I6" t="n">
         <v>89</v>
       </c>
       <c r="J6" t="n">
-        <v>1453</v>
+        <v>1128</v>
       </c>
       <c r="K6" t="n">
         <v>455</v>
@@ -1405,20 +1441,12 @@
         <v>5607</v>
       </c>
       <c r="M6" t="n">
-        <v>28414</v>
+        <v>22939</v>
       </c>
       <c r="N6" t="n">
         <v>-649356</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1453,13 +1481,13 @@
         <v>-15960</v>
       </c>
       <c r="H7" t="n">
-        <v>-35832</v>
+        <v>-20526</v>
       </c>
       <c r="I7" t="n">
         <v>558</v>
       </c>
       <c r="J7" t="n">
-        <v>3746</v>
+        <v>1885</v>
       </c>
       <c r="K7" t="n">
         <v>1462</v>
@@ -1468,20 +1496,12 @@
         <v>26695</v>
       </c>
       <c r="M7" t="n">
-        <v>131950</v>
+        <v>105728</v>
       </c>
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
-      <c r="O7" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1490,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1504,47 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0.65</v>
+        <v>1635</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-1.21</v>
       </c>
       <c r="F8" t="n">
-        <v>152254</v>
+        <v>3927</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-5151</v>
+        <v>-197</v>
       </c>
       <c r="H8" t="n">
-        <v>-38823</v>
+        <v>-96</v>
       </c>
       <c r="I8" t="n">
-        <v>-129</v>
+        <v>839</v>
       </c>
       <c r="J8" t="n">
-        <v>-38335</v>
+        <v>604</v>
       </c>
       <c r="K8" t="n">
-        <v>6447</v>
+        <v>265</v>
       </c>
       <c r="L8" t="n">
-        <v>119784</v>
+        <v>2225</v>
       </c>
       <c r="M8" t="n">
-        <v>639196</v>
+        <v>9540</v>
       </c>
       <c r="N8" t="n">
-        <v>-1122836</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-5.79</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140215</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1553,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1567,47 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2785</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>-4.3</v>
+        <v>1625</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.62</v>
       </c>
       <c r="F9" t="n">
-        <v>3755</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>-460</v>
+        <v>3136</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>382</v>
       </c>
       <c r="H9" t="n">
-        <v>62</v>
+        <v>-1117</v>
       </c>
       <c r="I9" t="n">
-        <v>-31</v>
+        <v>180</v>
       </c>
       <c r="J9" t="n">
-        <v>559</v>
+        <v>1160</v>
       </c>
       <c r="K9" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="L9" t="n">
-        <v>1885</v>
+        <v>2591</v>
       </c>
       <c r="M9" t="n">
-        <v>9748</v>
+        <v>11319</v>
       </c>
       <c r="N9" t="n">
-        <v>-89570</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106305</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1616,12 +1620,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1630,47 +1634,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2110</v>
+        <v>2785</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-0.24</v>
+        <v>-4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>2405</v>
+        <v>3755</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-165</v>
+        <v>-460</v>
       </c>
       <c r="H10" t="n">
-        <v>-1288</v>
+        <v>86</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>-31</v>
       </c>
       <c r="J10" t="n">
-        <v>1163</v>
+        <v>447</v>
       </c>
       <c r="K10" t="n">
-        <v>91</v>
+        <v>229</v>
       </c>
       <c r="L10" t="n">
-        <v>4020</v>
+        <v>1885</v>
       </c>
       <c r="M10" t="n">
-        <v>20629</v>
+        <v>7743</v>
       </c>
       <c r="N10" t="n">
-        <v>-19445</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89570</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1679,61 +1675,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1710</v>
+        <v>2110</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-0.58</v>
+        <v>-0.24</v>
       </c>
       <c r="F11" t="n">
-        <v>4226</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>39</v>
+        <v>2405</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>-165</v>
       </c>
       <c r="H11" t="n">
-        <v>-246</v>
+        <v>-687</v>
       </c>
       <c r="I11" t="n">
-        <v>-30</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>605</v>
+        <v>934</v>
       </c>
       <c r="K11" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="L11" t="n">
-        <v>-67</v>
+        <v>4020</v>
       </c>
       <c r="M11" t="n">
-        <v>171</v>
+        <v>16384</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19445</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1742,61 +1730,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>379</v>
+        <v>7675</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-4.41</v>
+        <v>-3.03</v>
       </c>
       <c r="F12" t="n">
-        <v>1998</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>-261</v>
+        <v>127</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>39</v>
       </c>
       <c r="H12" t="n">
-        <v>2589</v>
+        <v>59</v>
       </c>
       <c r="I12" t="n">
-        <v>-20</v>
+        <v>-43</v>
       </c>
       <c r="J12" t="n">
-        <v>2120</v>
+        <v>-81</v>
       </c>
       <c r="K12" t="n">
-        <v>-38</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>-330</v>
+        <v>296</v>
       </c>
       <c r="M12" t="n">
-        <v>-1563</v>
+        <v>1143</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8985</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1805,61 +1785,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1635</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-1.21</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>3927</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>-197</v>
+        <v>2730</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>39</v>
       </c>
       <c r="H13" t="n">
-        <v>-124</v>
+        <v>-41</v>
       </c>
       <c r="I13" t="n">
-        <v>839</v>
+        <v>-30</v>
       </c>
       <c r="J13" t="n">
-        <v>718</v>
+        <v>603</v>
       </c>
       <c r="K13" t="n">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="L13" t="n">
-        <v>2225</v>
+        <v>-67</v>
       </c>
       <c r="M13" t="n">
-        <v>11726</v>
+        <v>247</v>
       </c>
       <c r="N13" t="n">
-        <v>-140215</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1868,12 +1840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1882,44 +1854,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>875</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2.46</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>678</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>-78</v>
+        <v>-261</v>
       </c>
       <c r="H14" t="n">
-        <v>-77</v>
+        <v>2822</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-20</v>
       </c>
       <c r="J14" t="n">
-        <v>-4</v>
+        <v>1952</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>-38</v>
       </c>
       <c r="L14" t="n">
-        <v>21</v>
+        <v>-330</v>
       </c>
       <c r="M14" t="n">
-        <v>-546</v>
+        <v>-1164</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1942,22 +1909,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>900</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-7.02</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>1017</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>68</v>
       </c>
       <c r="H15" t="n">
-        <v>-2309</v>
+        <v>-689</v>
       </c>
       <c r="J15" t="n">
-        <v>5028</v>
+        <v>3517</v>
       </c>
       <c r="K15" t="n">
         <v>20</v>
@@ -1966,20 +1933,12 @@
         <v>-154</v>
       </c>
       <c r="M15" t="n">
-        <v>-377</v>
+        <v>-403</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1988,289 +1947,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>267.5</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2.88</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>7679</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>-522</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>76</v>
       </c>
       <c r="H16" t="n">
-        <v>613</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="J16" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="K16" t="n">
-        <v>123</v>
+        <v>-13</v>
       </c>
       <c r="L16" t="n">
-        <v>7131</v>
+        <v>-77</v>
       </c>
       <c r="M16" t="n">
-        <v>31501</v>
+        <v>109</v>
       </c>
       <c r="N16" t="n">
-        <v>-59005</v>
-      </c>
-      <c r="O16" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="F17" t="n">
-        <v>27817</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>3951</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-6224</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>14</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8630</v>
-      </c>
-      <c r="M17" t="n">
-        <v>38549</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-145084</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4582</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>-169</v>
-      </c>
-      <c r="H18" t="n">
-        <v>6571</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>8403</v>
-      </c>
-      <c r="M18" t="n">
-        <v>40718</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-98937</v>
-      </c>
-      <c r="O18" t="n">
-        <v>21.08</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>7675</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>-3.03</v>
-      </c>
-      <c r="E19" t="n">
-        <v>127</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G19" t="n">
-        <v>98</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-43</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-124</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>296</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1439</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-8985</v>
-      </c>
-      <c r="N19" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1625</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3136</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>382</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-735</v>
-      </c>
-      <c r="H20" t="n">
-        <v>180</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1340</v>
-      </c>
-      <c r="J20" t="n">
-        <v>192</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2591</v>
-      </c>
-      <c r="L20" t="n">
-        <v>13910</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-106305</v>
-      </c>
-      <c r="N20" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260330.xlsx
+++ b/outputs/monitor_xlsx/20260330.xlsx
@@ -544,10 +544,6 @@
           <t>-1.80%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-1.42%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-2.25%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+0.76%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.16%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>-4.23%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-1.42%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+3.25%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-639.37億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-166.09億</t>
@@ -807,7 +769,6 @@
           <t>32.07億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>22.6億</t>
@@ -818,8 +779,6 @@
           <t>113.0億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.91%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-741.29億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>8340口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8159口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>6.01億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-3.35億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1994,6 +1937,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>409</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1846</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="G17" t="n">
+        <v>161</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>38</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7560</v>
+      </c>
+      <c r="L17" t="n">
+        <v>39384</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22103</v>
+      </c>
+      <c r="N17" t="n">
+        <v>24.47</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260330.xlsx
+++ b/outputs/monitor_xlsx/20260330.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-1.47</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>175515</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-70742</v>
       </c>
       <c r="H4" t="n">
-        <v>-115466</v>
+        <v>-186208</v>
       </c>
       <c r="I4" t="n">
         <v>1900</v>
       </c>
       <c r="J4" t="n">
-        <v>-1770</v>
+        <v>130</v>
       </c>
       <c r="K4" t="n">
         <v>47712</v>
@@ -1274,11 +1273,14 @@
         <v>14406</v>
       </c>
       <c r="M4" t="n">
-        <v>52790</v>
+        <v>67196</v>
       </c>
       <c r="N4" t="n">
         <v>-4579297</v>
       </c>
+      <c r="O4" t="n">
+        <v>-2.74</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1301,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>834</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-3.58</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>2516</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>304</v>
       </c>
       <c r="H5" t="n">
-        <v>-1011</v>
+        <v>-708</v>
       </c>
       <c r="I5" t="n">
         <v>-437</v>
       </c>
       <c r="J5" t="n">
-        <v>-418</v>
+        <v>-855</v>
       </c>
       <c r="K5" t="n">
         <v>112</v>
@@ -1329,11 +1331,14 @@
         <v>2785</v>
       </c>
       <c r="M5" t="n">
-        <v>11154</v>
+        <v>13939</v>
       </c>
       <c r="N5" t="n">
         <v>-78891</v>
       </c>
+      <c r="O5" t="n">
+        <v>-8.43</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1356,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1485</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-1.66</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>11853</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>-842</v>
       </c>
       <c r="H6" t="n">
-        <v>4728</v>
+        <v>3886</v>
       </c>
       <c r="I6" t="n">
         <v>89</v>
       </c>
       <c r="J6" t="n">
-        <v>1128</v>
+        <v>1217</v>
       </c>
       <c r="K6" t="n">
         <v>455</v>
@@ -1384,11 +1389,14 @@
         <v>5607</v>
       </c>
       <c r="M6" t="n">
-        <v>22939</v>
+        <v>28546</v>
       </c>
       <c r="N6" t="n">
         <v>-649356</v>
       </c>
+      <c r="O6" t="n">
+        <v>6.09</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1411,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1780</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>46272</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-15960</v>
       </c>
       <c r="H7" t="n">
-        <v>-20526</v>
+        <v>-36486</v>
       </c>
       <c r="I7" t="n">
         <v>558</v>
       </c>
       <c r="J7" t="n">
-        <v>1885</v>
+        <v>2443</v>
       </c>
       <c r="K7" t="n">
         <v>1462</v>
@@ -1439,11 +1447,14 @@
         <v>26695</v>
       </c>
       <c r="M7" t="n">
-        <v>105728</v>
+        <v>132423</v>
       </c>
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
+      <c r="O7" t="n">
+        <v>-4.19</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1635</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-1.21</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>3927</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-197</v>
       </c>
       <c r="H8" t="n">
-        <v>-96</v>
+        <v>-293</v>
       </c>
       <c r="I8" t="n">
         <v>839</v>
       </c>
       <c r="J8" t="n">
-        <v>604</v>
+        <v>1443</v>
       </c>
       <c r="K8" t="n">
         <v>265</v>
@@ -1494,11 +1505,14 @@
         <v>2225</v>
       </c>
       <c r="M8" t="n">
-        <v>9540</v>
+        <v>11765</v>
       </c>
       <c r="N8" t="n">
         <v>-140215</v>
       </c>
+      <c r="O8" t="n">
+        <v>8.17</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1521,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1625</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0.62</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>3136</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>382</v>
       </c>
       <c r="H9" t="n">
-        <v>-1117</v>
+        <v>-735</v>
       </c>
       <c r="I9" t="n">
         <v>180</v>
       </c>
       <c r="J9" t="n">
-        <v>1160</v>
+        <v>1340</v>
       </c>
       <c r="K9" t="n">
         <v>192</v>
@@ -1549,11 +1563,14 @@
         <v>2591</v>
       </c>
       <c r="M9" t="n">
-        <v>11319</v>
+        <v>13910</v>
       </c>
       <c r="N9" t="n">
         <v>-106305</v>
       </c>
+      <c r="O9" t="n">
+        <v>9.039999999999999</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1576,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2785</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-4.3</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3755</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-460</v>
       </c>
       <c r="H10" t="n">
-        <v>86</v>
+        <v>-374</v>
       </c>
       <c r="I10" t="n">
         <v>-31</v>
       </c>
       <c r="J10" t="n">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="K10" t="n">
         <v>229</v>
@@ -1604,11 +1621,14 @@
         <v>1885</v>
       </c>
       <c r="M10" t="n">
-        <v>7743</v>
+        <v>9628</v>
       </c>
       <c r="N10" t="n">
         <v>-89570</v>
       </c>
+      <c r="O10" t="n">
+        <v>6.73</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1631,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2110</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-0.24</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>2405</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-165</v>
       </c>
       <c r="H11" t="n">
-        <v>-687</v>
+        <v>-852</v>
       </c>
       <c r="I11" t="n">
         <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="K11" t="n">
         <v>91</v>
@@ -1659,11 +1679,14 @@
         <v>4020</v>
       </c>
       <c r="M11" t="n">
-        <v>16384</v>
+        <v>20404</v>
       </c>
       <c r="N11" t="n">
         <v>-19445</v>
       </c>
+      <c r="O11" t="n">
+        <v>9.970000000000001</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1686,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>7675</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-3.03</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>127</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>39</v>
       </c>
       <c r="H12" t="n">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="I12" t="n">
         <v>-43</v>
       </c>
       <c r="J12" t="n">
-        <v>-81</v>
+        <v>-124</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
@@ -1714,11 +1737,14 @@
         <v>296</v>
       </c>
       <c r="M12" t="n">
-        <v>1143</v>
+        <v>1439</v>
       </c>
       <c r="N12" t="n">
         <v>-8985</v>
       </c>
+      <c r="O12" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1741,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>39</v>
       </c>
       <c r="H13" t="n">
-        <v>-41</v>
+        <v>-2</v>
       </c>
       <c r="I13" t="n">
         <v>-30</v>
       </c>
       <c r="J13" t="n">
-        <v>603</v>
+        <v>573</v>
       </c>
       <c r="K13" t="n">
         <v>121</v>
@@ -1769,11 +1795,14 @@
         <v>-67</v>
       </c>
       <c r="M13" t="n">
-        <v>247</v>
+        <v>180</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1796,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-261</v>
       </c>
       <c r="H14" t="n">
-        <v>2822</v>
+        <v>2561</v>
       </c>
       <c r="I14" t="n">
         <v>-20</v>
       </c>
       <c r="J14" t="n">
-        <v>1952</v>
+        <v>1932</v>
       </c>
       <c r="K14" t="n">
         <v>-38</v>
@@ -1824,11 +1853,14 @@
         <v>-330</v>
       </c>
       <c r="M14" t="n">
-        <v>-1164</v>
+        <v>-1494</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1851,20 +1883,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>68</v>
       </c>
       <c r="H15" t="n">
-        <v>-689</v>
+        <v>-621</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>3517</v>
@@ -1876,11 +1911,14 @@
         <v>-154</v>
       </c>
       <c r="M15" t="n">
-        <v>-403</v>
+        <v>-557</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1903,20 +1941,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>76</v>
       </c>
       <c r="H16" t="n">
-        <v>96</v>
+        <v>171</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-10</v>
@@ -1928,11 +1969,14 @@
         <v>-77</v>
       </c>
       <c r="M16" t="n">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1950,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>409</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>1846</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>208</v>
       </c>
-      <c r="G17" t="n">
-        <v>161</v>
-      </c>
       <c r="H17" t="n">
+        <v>233</v>
+      </c>
+      <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
-        <v>-3</v>
-      </c>
       <c r="J17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K17" t="n">
         <v>38</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>7560</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>39384</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-22103</v>
       </c>
-      <c r="N17" t="n">
-        <v>24.47</v>
+      <c r="O17" t="n">
+        <v>23.31</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260330.xlsx
+++ b/outputs/monitor_xlsx/20260330.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>23.31</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-4.73</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8234</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-1259</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-3578</v>
+      </c>
+      <c r="I18" t="n">
+        <v>96</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1325</v>
+      </c>
+      <c r="K18" t="n">
+        <v>498</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6268</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31093</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400973</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-10.69</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>493.5</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5105</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-1155</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2665</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-632</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2459</v>
+      </c>
+      <c r="K19" t="n">
+        <v>204</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30925</v>
+      </c>
+      <c r="M19" t="n">
+        <v>156870</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393878</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>580</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="F20" t="n">
+        <v>19641</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>2896</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3963</v>
+      </c>
+      <c r="I20" t="n">
+        <v>576</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5434</v>
+      </c>
+      <c r="K20" t="n">
+        <v>556</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8547</v>
+      </c>
+      <c r="M20" t="n">
+        <v>46212</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160878</v>
+      </c>
+      <c r="O20" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
